--- a/JsonConverter/ExcelFiles/0_NomalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NomalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_86877D79C9AF0319605F5B8E85B6E9117C892375" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F3AED-CC82-499B-9374-A4B8E270CCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="1050" windowWidth="15465" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? &lt;np&gt;사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
   </si>
@@ -31,106 +31,114 @@
     <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..&lt;np&gt;그리고 무엇보다 내가 너를 더이상 좋아하지 않는다는 감정이 들었어. &lt;np&gt;얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.&lt;np&gt; 근데 오늘 느낀 감정은 그냥 다른 친구들이 한 행동처럼 '음 그럴 수 있지,' 라고 느꼈어.. &lt;np&gt;이런 감정에서 나는 너에 대한 애정이 식었고, 2달전부터 해온 생각들이 틀리지 않았음을 직감했어.</t>
   </si>
   <si>
+    <t>SelectionNameList</t>
+  </si>
+  <si>
+    <t>CharacterDataId</t>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>VoicePath</t>
+  </si>
+  <si>
+    <t>TexturePath</t>
+  </si>
+  <si>
+    <t>고유 ID</t>
+  </si>
+  <si>
+    <t>(name)</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_102</t>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+  </si>
+  <si>
+    <t>많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; 우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..&lt;np&gt;안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_105</t>
+  </si>
+  <si>
+    <t>아니? 내 생각은 달라. &lt;np&gt;우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아.. &lt;np&gt;내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어. &lt;np&gt;그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_103</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_104</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_108</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_107</t>
+  </si>
+  <si>
+    <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_109</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_110</t>
+  </si>
+  <si>
+    <t>우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? &lt;np&gt;물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
+  </si>
+  <si>
+    <t>정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... &lt;np&gt;하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네..&lt;np&gt;내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_101</t>
+  </si>
+  <si>
+    <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_106</t>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.&lt;np&gt; 그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아...&lt;np&gt;갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>요즘 우리는 서로 매우 바쁜 삶을 살고 있고, 전에 말했던 헤어짐의 타이밍이지 않을까 싶어. 가장 힘들지 않게 이별 할 수 있는 기회라고 생각했어.</t>
-  </si>
-  <si>
-    <t>SelectionNameList</t>
-  </si>
-  <si>
-    <t>CharacterDataId</t>
-  </si>
-  <si>
-    <t>NextDialogueId</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>VoicePath</t>
-  </si>
-  <si>
-    <t>TexturePath</t>
-  </si>
-  <si>
-    <t>고유 ID</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_102</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomalDialogue_opening_1_1_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>......</t>
-  </si>
-  <si>
-    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.&lt;np&gt; 그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아...&lt;np&gt;갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
-  </si>
-  <si>
-    <t>character_Player_01</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_100</t>
-  </si>
-  <si>
-    <t>많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; 우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..&lt;np&gt;안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
-  </si>
-  <si>
-    <t>character_Minhyeong_01</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_105</t>
-  </si>
-  <si>
-    <t>아니? 내 생각은 달라. &lt;np&gt;우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아.. &lt;np&gt;내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어. &lt;np&gt;그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_103</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_104</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_108</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_107</t>
-  </si>
-  <si>
-    <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_109</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_110</t>
-  </si>
-  <si>
-    <t>우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? &lt;np&gt;물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
-  </si>
-  <si>
-    <t>정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... &lt;np&gt;하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네..&lt;np&gt;내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_101</t>
-  </si>
-  <si>
-    <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_106</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -479,7 +487,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -491,84 +499,84 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -577,13 +585,13 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -593,16 +601,16 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -611,10 +619,10 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>2</v>
@@ -627,16 +635,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -645,13 +653,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -661,16 +669,16 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -679,16 +687,16 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -697,13 +705,13 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -713,16 +721,16 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -731,13 +739,13 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>

--- a/JsonConverter/ExcelFiles/0_NomalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NomalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F3AED-CC82-499B-9374-A4B8E270CCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79E998E-B6AC-4D4E-A526-59ABD83C2CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2775" yWindow="945" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? &lt;np&gt;사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
   </si>
@@ -37,9 +37,6 @@
     <t>CharacterDataId</t>
   </si>
   <si>
-    <t>NextDialogueId</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_102</t>
-  </si>
-  <si>
     <t>character_Player_01</t>
   </si>
   <si>
@@ -79,50 +73,19 @@
     <t>character_Minhyeong_01</t>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_105</t>
-  </si>
-  <si>
     <t>아니? 내 생각은 달라. &lt;np&gt;우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아.. &lt;np&gt;내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어. &lt;np&gt;그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_103</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_104</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_108</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_107</t>
-  </si>
-  <si>
     <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_109</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_110</t>
-  </si>
-  <si>
     <t>우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? &lt;np&gt;물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
   </si>
   <si>
     <t>정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... &lt;np&gt;하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네..&lt;np&gt;내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_101</t>
-  </si>
-  <si>
     <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_106</t>
-  </si>
-  <si>
-    <t>nomalDialogue_opening_1_1_100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.&lt;np&gt; 그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아...&lt;np&gt;갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
@@ -133,11 +96,78 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>nomalDialogue_opening_1_1_101</t>
+    <t>......</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>......</t>
+    <t>normalDialogue_opening_1_1_104</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_106</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_111</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_113</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_114</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_116</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_117</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_118</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_120</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_opening_1_1_121</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_107</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_112</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_115</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_119</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_122</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -480,14 +510,16 @@
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="6" width="77.140625" customWidth="1"/>
+    <col min="1" max="1" width="43.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="4" max="6" width="77.140625" customWidth="1"/>
     <col min="7" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -499,84 +531,84 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -585,15 +617,17 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -601,16 +635,16 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -619,15 +653,17 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -635,16 +671,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -653,15 +689,17 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -669,16 +707,16 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -687,16 +725,16 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -705,15 +743,17 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -721,16 +761,16 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -739,15 +779,17 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
